--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/28,07,26 Останкино СЫРЫ/дв 28,07,26 млрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/28,07,26 Останкино СЫРЫ/дв 28,07,26 млрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\28,07,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43E0F7A-E128-4446-AAC6-DC06C53B4C85}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE9759F-D3E2-4873-A35F-2E7197CD2A27}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="89">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -297,6 +297,9 @@
   <si>
     <t>03,08,</t>
   </si>
+  <si>
+    <t>30,07,26 - нет на заводе</t>
+  </si>
 </sst>
 </file>
 
@@ -350,7 +353,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +385,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -436,6 +445,8 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1101,7 +1112,7 @@
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>590</v>
+        <v>398</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1307,9 +1318,8 @@
       <c r="Q7" s="5">
         <v>100</v>
       </c>
-      <c r="R7" s="5">
-        <f>VLOOKUP(A7,заказ!A:B,2,0)</f>
-        <v>96</v>
+      <c r="R7" s="14">
+        <v>0</v>
       </c>
       <c r="S7" s="1" t="e">
         <f t="shared" si="4"/>
@@ -1346,7 +1356,9 @@
       <c r="AC7" s="1">
         <v>0</v>
       </c>
-      <c r="AD7" s="1"/>
+      <c r="AD7" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="AE7" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -1411,9 +1423,8 @@
       <c r="Q8" s="5">
         <v>100</v>
       </c>
-      <c r="R8" s="5">
-        <f>VLOOKUP(A8,заказ!A:B,2,0)</f>
-        <v>96</v>
+      <c r="R8" s="14">
+        <v>0</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" si="4"/>
@@ -1450,7 +1461,9 @@
       <c r="AC8" s="1">
         <v>0</v>
       </c>
-      <c r="AD8" s="1"/>
+      <c r="AD8" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="AE8" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
